--- a/dati_wheatstone.xlsx
+++ b/dati_wheatstone.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Computer\Università\Lab. Fisica 2\Esperienze\2° Esperienza\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C24C99-47EA-4CE4-AD26-E3B1A7BD356B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F7ECA0-86B3-4EB3-864A-8F4C12E82AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -196,7 +196,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -477,10 +477,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -494,14 +494,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>240</v>
       </c>
       <c r="B2">
         <v>8</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <f>(A2)*1/100</f>
         <v>2.4</v>
       </c>
@@ -509,7 +509,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>A2+10</f>
         <v>250</v>
@@ -517,7 +517,7 @@
       <c r="B3">
         <v>6</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <f t="shared" ref="C3:C9" si="0">(A3)*1/100</f>
         <v>2.5</v>
       </c>
@@ -525,7 +525,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <f t="shared" ref="A4:A9" si="1">A3+10</f>
         <v>260</v>
@@ -533,7 +533,7 @@
       <c r="B4">
         <v>4</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <f t="shared" si="0"/>
         <v>2.6</v>
       </c>
@@ -541,7 +541,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <f t="shared" si="1"/>
         <v>270</v>
@@ -549,16 +549,15 @@
       <c r="B5">
         <v>1.5</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <f t="shared" si="0"/>
         <v>2.7</v>
       </c>
       <c r="D5">
         <v>0.3</v>
       </c>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" si="1"/>
         <v>280</v>
@@ -566,7 +565,7 @@
       <c r="B6">
         <v>-1.5</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <f t="shared" si="0"/>
         <v>2.8</v>
       </c>
@@ -574,7 +573,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" si="1"/>
         <v>290</v>
@@ -582,7 +581,7 @@
       <c r="B7">
         <v>-3.5</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <f t="shared" si="0"/>
         <v>2.9</v>
       </c>
@@ -590,7 +589,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" si="1"/>
         <v>300</v>
@@ -598,7 +597,7 @@
       <c r="B8">
         <v>-6</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -606,7 +605,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" si="1"/>
         <v>310</v>
@@ -614,7 +613,7 @@
       <c r="B9">
         <v>-8</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <f t="shared" si="0"/>
         <v>3.1</v>
       </c>
